--- a/artfynd/A 25231-2023 artfynd.xlsx
+++ b/artfynd/A 25231-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25231-2023 artfynd.xlsx
+++ b/artfynd/A 25231-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31495</v>
+        <v>114307232</v>
       </c>
       <c r="B2" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100084</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korset, NO Strömsrum, Sm</t>
+          <t>Strömsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588714.9803412976</v>
+        <v>588780</v>
       </c>
       <c r="R2" t="n">
-        <v>6312496.67622795</v>
+        <v>6312478</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,45 +754,1991 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4m S. Calluna AB. Boxen sitter på en ung tall. Produktionsskog, sommarhus.</t>
+        </is>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>31495</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Korset, NO Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>588715</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6312497</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>1990-04-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>1990-04-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr">
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Boris Berglund</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Boris Berglund</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>107096455</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56822</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Calluna Ab</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107096441</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56827</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100087</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fransfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Myotis nattereri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Calluna Ab</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98571431</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>588806</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6312481</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Strömsrum. Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>107096394</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Calluna Ab</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98571459</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>588806</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6312481</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Strömsrum. Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>107096426</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Calluna Ab</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98571477</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>588806</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6312481</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Strömsrum. Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>107096448</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>98571449</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>588806</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6312481</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Strömsrum. Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>107096413</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>98571439</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>588806</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6312481</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Strömsrum. Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>107096401</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Calluna Ab</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>107096383</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>98571413</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>588806</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6312481</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Strömsrum. Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25231-2023 artfynd.xlsx
+++ b/artfynd/A 25231-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1697,62 +1697,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98571477</v>
+        <v>134691937</v>
       </c>
       <c r="B10" t="n">
-        <v>56823</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205992</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömsrum, Sm</t>
+          <t>Skuteholm, Skuteholm, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588806</v>
+        <v>589076</v>
       </c>
       <c r="R10" t="n">
-        <v>6312481</v>
+        <v>6312239</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1776,27 +1767,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Strömsrum. Calluna AB</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,23 +1787,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107096448</v>
+        <v>98571477</v>
       </c>
       <c r="B11" t="n">
         <v>56823</v>
@@ -1857,7 +1829,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1876,13 +1848,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588780</v>
+        <v>588806</v>
       </c>
       <c r="R11" t="n">
-        <v>6312478</v>
+        <v>6312481</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1906,7 +1878,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1916,17 +1888,17 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>CallunaAB</t>
+          <t>Strömsrum. Calluna AB</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1946,7 +1918,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lara Millon</t>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1957,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98571449</v>
+        <v>107096448</v>
       </c>
       <c r="B12" t="n">
-        <v>56835</v>
+        <v>56823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,26 +1940,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2006,13 +1978,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588806</v>
+        <v>588780</v>
       </c>
       <c r="R12" t="n">
-        <v>6312481</v>
+        <v>6312478</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2036,7 +2008,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2046,17 +2018,17 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Strömsrum. Calluna AB</t>
+          <t>CallunaAB</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2076,7 +2048,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+          <t>Lara Millon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2087,7 +2059,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107096413</v>
+        <v>98571449</v>
       </c>
       <c r="B13" t="n">
         <v>56835</v>
@@ -2117,7 +2089,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2136,13 +2108,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588780</v>
+        <v>588806</v>
       </c>
       <c r="R13" t="n">
-        <v>6312478</v>
+        <v>6312481</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2166,7 +2138,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2176,17 +2148,17 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>CallunaAB</t>
+          <t>Strömsrum. Calluna AB</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2206,7 +2178,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lara Millon</t>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2217,37 +2189,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98571439</v>
+        <v>107096413</v>
       </c>
       <c r="B14" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2266,13 +2238,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588806</v>
+        <v>588780</v>
       </c>
       <c r="R14" t="n">
-        <v>6312481</v>
+        <v>6312478</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2296,7 +2268,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2306,17 +2278,17 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Strömsrum. Calluna AB</t>
+          <t>CallunaAB</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2336,7 +2308,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
+          <t>Lara Millon</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2347,7 +2319,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107096401</v>
+        <v>98571439</v>
       </c>
       <c r="B15" t="n">
         <v>56816</v>
@@ -2377,7 +2349,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2396,13 +2368,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588780</v>
+        <v>588806</v>
       </c>
       <c r="R15" t="n">
-        <v>6312478</v>
+        <v>6312481</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2426,7 +2398,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2436,17 +2408,17 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Calluna Ab</t>
+          <t>Strömsrum. Calluna AB</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2466,7 +2438,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lara Millon</t>
+          <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2477,37 +2449,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107096383</v>
+        <v>107096401</v>
       </c>
       <c r="B16" t="n">
-        <v>56840</v>
+        <v>56816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206000</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2576,7 +2548,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>CallunaAB</t>
+          <t>Calluna Ab</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2589,11 +2561,6 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>Karin Gerell Lundberg</t>
-        </is>
-      </c>
       <c r="AW16" t="inlineStr">
         <is>
           <t>Marielle Gustafsson</t>
@@ -2612,129 +2579,264 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>107096383</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strömsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>588780</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6312478</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>CallunaAB</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lara Millon</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>98571413</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>56837</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NT</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>206002</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Brunlångöra</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Plecotus auritus</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>registreringar</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>autobox med tidsexpansion</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Strömsrum, Sm</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q18" t="n">
         <v>588806</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>6312481</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>10</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Kalmar</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Mönsterås</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Småland</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Ålem</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Strömsrum. Calluna AB</t>
         </is>
       </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
         <is>
           <t>Marielle Gustafsson</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Alexander Eriksson, Emily Macgregor, Lara Millon</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>

--- a/artfynd/A 25231-2023 artfynd.xlsx
+++ b/artfynd/A 25231-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114307232</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/31495</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096455</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1174,6 +1194,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096441</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1304,6 +1329,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571431</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1434,6 +1464,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096394</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1564,6 +1599,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571459</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1694,6 +1734,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096426</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1796,6 +1841,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134691937</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1926,6 +1976,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571477</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2056,6 +2111,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096448</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2186,6 +2246,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571449</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2316,6 +2381,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096413</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2446,6 +2516,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571439</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2576,6 +2651,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096401</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2711,6 +2791,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096383</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2841,8 +2926,32 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>